--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:17</t>
+    <t xml:space="preserve">2026-09-09 18:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 18:54</t>
+    <t xml:space="preserve">2026-09-17 04:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:14</t>
+    <t xml:space="preserve">2026-09-25 11:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:08</t>
+    <t xml:space="preserve">2026-09-26 23:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2018_coquimbo.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:43</t>
+    <t xml:space="preserve">2026-10-05 04:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
